--- a/results/0916-all/滇南农林区/tech_selected_summary.xlsx
+++ b/results/0916-all/滇南农林区/tech_selected_summary.xlsx
@@ -148,94 +148,94 @@
     <t>镇沅彝族哈尼族拉祜族自治县</t>
   </si>
   <si>
-    <t>县名</t>
-  </si>
-  <si>
-    <t>技术1</t>
-  </si>
-  <si>
-    <t>技术2</t>
-  </si>
-  <si>
-    <t>技术3</t>
-  </si>
-  <si>
-    <t>技术4</t>
-  </si>
-  <si>
-    <t>技术5</t>
-  </si>
-  <si>
-    <t>技术6</t>
-  </si>
-  <si>
-    <t>技术7</t>
-  </si>
-  <si>
-    <t>技术8</t>
-  </si>
-  <si>
-    <t>技术9</t>
-  </si>
-  <si>
-    <t>技术10</t>
-  </si>
-  <si>
-    <t>技术11</t>
-  </si>
-  <si>
-    <t>技术12</t>
-  </si>
-  <si>
-    <t>技术13</t>
-  </si>
-  <si>
-    <t>技术14</t>
-  </si>
-  <si>
-    <t>技术15</t>
-  </si>
-  <si>
-    <t>技术16</t>
-  </si>
-  <si>
-    <t>技术17</t>
-  </si>
-  <si>
-    <t>技术18</t>
-  </si>
-  <si>
-    <t>技术19</t>
-  </si>
-  <si>
-    <t>技术20</t>
-  </si>
-  <si>
-    <t>技术21</t>
-  </si>
-  <si>
-    <t>技术22</t>
-  </si>
-  <si>
-    <t>技术23</t>
-  </si>
-  <si>
-    <t>技术24</t>
-  </si>
-  <si>
-    <t>总经济成本</t>
+    <t>Counties</t>
+  </si>
+  <si>
+    <t>Tech1</t>
+  </si>
+  <si>
+    <t>Tech2</t>
+  </si>
+  <si>
+    <t>Tech3</t>
+  </si>
+  <si>
+    <t>Tech4</t>
+  </si>
+  <si>
+    <t>Tech5</t>
+  </si>
+  <si>
+    <t>Tech6</t>
+  </si>
+  <si>
+    <t>Tech7</t>
+  </si>
+  <si>
+    <t>Tech8</t>
+  </si>
+  <si>
+    <t>Tech9</t>
+  </si>
+  <si>
+    <t>Tech10</t>
+  </si>
+  <si>
+    <t>Tech11</t>
+  </si>
+  <si>
+    <t>Tech12</t>
+  </si>
+  <si>
+    <t>Tech13</t>
+  </si>
+  <si>
+    <t>Tech14</t>
+  </si>
+  <si>
+    <t>Tech15</t>
+  </si>
+  <si>
+    <t>Tech16</t>
+  </si>
+  <si>
+    <t>Tech17</t>
+  </si>
+  <si>
+    <t>Tech18</t>
+  </si>
+  <si>
+    <t>Tech19</t>
+  </si>
+  <si>
+    <t>Tech20</t>
+  </si>
+  <si>
+    <t>Tech21</t>
+  </si>
+  <si>
+    <t>Tech22</t>
+  </si>
+  <si>
+    <t>Tech23</t>
+  </si>
+  <si>
+    <t>Tech24</t>
+  </si>
+  <si>
+    <t>Total economic cost</t>
   </si>
   <si>
     <t>Feed processing_dairy</t>
   </si>
   <si>
-    <t>总经济成本: 25479.30</t>
+    <t>25479.30</t>
   </si>
   <si>
     <t>EEF(CRF)_maize</t>
   </si>
   <si>
-    <t>总经济成本: 17644225.11</t>
+    <t>17644225.11</t>
   </si>
   <si>
     <t>Cooling_pig</t>
@@ -268,10 +268,10 @@
     <t>irrigation (drip irrigation)_vegetable</t>
   </si>
   <si>
-    <t>总经济成本: 56357044.43</t>
-  </si>
-  <si>
-    <t>总经济成本: 0.00</t>
+    <t>56357044.43</t>
+  </si>
+  <si>
+    <t>0.00</t>
   </si>
   <si>
     <t>Increasing byproduct_pig</t>
@@ -322,10 +322,10 @@
     <t>4R(Right rate)_rice</t>
   </si>
   <si>
-    <t>总经济成本: 62707654.13</t>
-  </si>
-  <si>
-    <t>总经济成本: 12512752.28</t>
+    <t>62707654.13</t>
+  </si>
+  <si>
+    <t>12512752.28</t>
   </si>
   <si>
     <t>Increasing feeding level_sheep &amp; goat</t>
@@ -346,31 +346,31 @@
     <t>cover crop (mix)_vegetable</t>
   </si>
   <si>
-    <t>总经济成本: 100903310.88</t>
+    <t>100903310.88</t>
   </si>
   <si>
     <t>compost（add)_vegetable</t>
   </si>
   <si>
-    <t>总经济成本: 49432841.36</t>
+    <t>49432841.36</t>
   </si>
   <si>
     <t>irrigation (AWD irrigation)_rice</t>
   </si>
   <si>
-    <t>总经济成本: 49852230.71</t>
-  </si>
-  <si>
-    <t>总经济成本: 115153995.29</t>
+    <t>49852230.71</t>
+  </si>
+  <si>
+    <t>115153995.29</t>
   </si>
   <si>
     <t>Composting_poultry</t>
   </si>
   <si>
-    <t>总经济成本: 73253876.93</t>
-  </si>
-  <si>
-    <t>总经济成本: 3148203.35</t>
+    <t>73253876.93</t>
+  </si>
+  <si>
+    <t>3148203.35</t>
   </si>
   <si>
     <t>chemical amendments_pig</t>
@@ -400,7 +400,7 @@
     <t>tillage management (zero tillage)_rice</t>
   </si>
   <si>
-    <t>总经济成本: 57486606.28</t>
+    <t>57486606.28</t>
   </si>
   <si>
     <t>4R(Right time)_rice</t>
@@ -409,19 +409,19 @@
     <t>tillage management (zero tillage)_maize</t>
   </si>
   <si>
-    <t>总经济成本: 44001860.77</t>
+    <t>44001860.77</t>
   </si>
   <si>
     <t>4R(Right type)_maize</t>
   </si>
   <si>
-    <t>总经济成本: 21987265.37</t>
+    <t>21987265.37</t>
   </si>
   <si>
     <t>rolller press_beef cattle</t>
   </si>
   <si>
-    <t>总经济成本: 126839527.62</t>
+    <t>126839527.62</t>
   </si>
   <si>
     <t>metal salt_Poultry</t>
@@ -436,31 +436,31 @@
     <t>cover crop (mix)_friut</t>
   </si>
   <si>
-    <t>总经济成本: 126764304.77</t>
+    <t>126764304.77</t>
   </si>
   <si>
     <t>EEF(NI)_rice</t>
   </si>
   <si>
-    <t>总经济成本: 89857623.85</t>
-  </si>
-  <si>
-    <t>总经济成本: 11818539.90</t>
+    <t>89857623.85</t>
+  </si>
+  <si>
+    <t>11818539.90</t>
   </si>
   <si>
     <t>Mixture additives _pig</t>
   </si>
   <si>
-    <t>总经济成本: 61369147.59</t>
-  </si>
-  <si>
-    <t>总经济成本: 77585503.55</t>
+    <t>61369147.59</t>
+  </si>
+  <si>
+    <t>77585503.55</t>
   </si>
   <si>
     <t>biochar_vegetable</t>
   </si>
   <si>
-    <t>总经济成本: 29445022.67</t>
+    <t>29445022.67</t>
   </si>
   <si>
     <t>Biochar_dairy</t>
@@ -469,19 +469,19 @@
     <t>rolller press_dairy</t>
   </si>
   <si>
-    <t>总经济成本: 69024929.25</t>
-  </si>
-  <si>
-    <t>总经济成本: 61350627.11</t>
-  </si>
-  <si>
-    <t>总经济成本: 96538456.92</t>
-  </si>
-  <si>
-    <t>总经济成本: 40351576.63</t>
-  </si>
-  <si>
-    <t>总经济成本: 16950.47</t>
+    <t>69024929.25</t>
+  </si>
+  <si>
+    <t>61350627.11</t>
+  </si>
+  <si>
+    <t>96538456.92</t>
+  </si>
+  <si>
+    <t>40351576.63</t>
+  </si>
+  <si>
+    <t>16950.47</t>
   </si>
 </sst>
 </file>
